--- a/Result/profitability/5355.xlsx
+++ b/Result/profitability/5355.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.26</v>
+        <v>-0.2275</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.1825</v>
+        <v>-12.96375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.24</v>
+        <v>-0.20875</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.7125</v>
+        <v>-7.98125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>-0.32</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.245</v>
+        <v>-0.24375</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.766249999999999</v>
+        <v>-7.09625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3025</v>
+        <v>-0.25375</v>
       </c>
       <c r="N5" t="n">
-        <v>-10.45375</v>
+        <v>-6.936249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3075</v>
+        <v>-0.26625</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.71</v>
+        <v>-6.64375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.31875</v>
+        <v>-0.285</v>
       </c>
       <c r="N7" t="n">
-        <v>-9.59</v>
+        <v>-7.7925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3225</v>
+        <v>-0.30875</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.01375</v>
+        <v>-6.788749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>168</v>
+      </c>
+      <c r="D75" t="n">
+        <v>155</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-15.41625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7857142857142858</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.781781781781782</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.38416133792425</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
